--- a/data/trans_dic/LAWTONB_2R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R3-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia moderada o superior</t>
+          <t>Población con dependencia moderada o superior (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 24,58</t>
+          <t>11,63; 24,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,72; 25,42</t>
+          <t>11,6; 24,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,03; 24,39</t>
+          <t>12,17; 24,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,06; 31,18</t>
+          <t>19,49; 31,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 24,16</t>
+          <t>11,86; 25,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,16; 34,55</t>
+          <t>20,29; 34,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 31,47</t>
+          <t>17,46; 31,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,68; 39,8</t>
+          <t>30,18; 39,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,84; 21,84</t>
+          <t>13,08; 22,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,64; 27,87</t>
+          <t>18,36; 27,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,95; 25,99</t>
+          <t>16,72; 25,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,96; 34,05</t>
+          <t>27,3; 34,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,09; 19,89</t>
+          <t>8,71; 20,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,57; 31,71</t>
+          <t>17,47; 31,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 22,51</t>
+          <t>11,15; 21,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,54; 22,91</t>
+          <t>14,09; 23,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,47; 27,4</t>
+          <t>14,92; 28,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,71; 38,17</t>
+          <t>24,76; 38,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,91; 32,64</t>
+          <t>19,25; 32,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,42; 33,95</t>
+          <t>25,39; 34,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,52; 21,94</t>
+          <t>13,47; 22,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,12; 33,59</t>
+          <t>23,18; 33,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 25,5</t>
+          <t>17,15; 26,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,03; 28,13</t>
+          <t>22,0; 28,52</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 19,06</t>
+          <t>5,55; 18,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 31,86</t>
+          <t>13,22; 31,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 19,4</t>
+          <t>7,14; 20,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 14,24</t>
+          <t>5,72; 14,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,44; 20,62</t>
+          <t>8,54; 20,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,6; 37,75</t>
+          <t>22,02; 38,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,82; 37,3</t>
+          <t>20,83; 37,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 26,78</t>
+          <t>3,03; 27,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 17,87</t>
+          <t>9,03; 17,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,7; 32,72</t>
+          <t>20,85; 32,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,51; 27,27</t>
+          <t>16,49; 27,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 18,51</t>
+          <t>4,05; 19,24</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 14,96</t>
+          <t>6,0; 14,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,95; 27,48</t>
+          <t>13,31; 27,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 18,57</t>
+          <t>8,61; 18,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 17,7</t>
+          <t>10,13; 18,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,49; 26,55</t>
+          <t>15,97; 26,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,21; 24,92</t>
+          <t>14,53; 24,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,92; 25,39</t>
+          <t>14,0; 25,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,38; 28,77</t>
+          <t>20,98; 28,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,5; 20,82</t>
+          <t>12,81; 20,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,95; 24,44</t>
+          <t>15,86; 23,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 20,74</t>
+          <t>13,25; 20,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,44; 23,12</t>
+          <t>17,42; 23,05</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,24; 15,93</t>
+          <t>10,21; 16,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 24,86</t>
+          <t>17,41; 24,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,58; 17,89</t>
+          <t>12,23; 17,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,43; 18,91</t>
+          <t>14,37; 19,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,58; 21,8</t>
+          <t>15,61; 21,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,05; 29,46</t>
+          <t>23,26; 30,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,19; 26,8</t>
+          <t>20,58; 27,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,7; 28,99</t>
+          <t>12,0; 29,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,09; 18,44</t>
+          <t>13,97; 18,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,25; 26,2</t>
+          <t>21,38; 26,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,88; 22,44</t>
+          <t>17,73; 22,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,22; 23,78</t>
+          <t>13,69; 23,87</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia moderada o superior</t>
+          <t>Población con dependencia moderada o superior (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12855; 28265</t>
+          <t>13368; 28563</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16355; 35479</t>
+          <t>16194; 34579</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16451; 33354</t>
+          <t>16634; 32855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29699; 46176</t>
+          <t>28859; 46498</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17728; 36127</t>
+          <t>17740; 38769</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33619; 57627</t>
+          <t>33845; 56929</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31231; 54572</t>
+          <t>30281; 54115</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54643; 70899</t>
+          <t>53761; 69617</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33964; 57781</t>
+          <t>34610; 58769</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54035; 85382</t>
+          <t>56249; 85398</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49452; 80610</t>
+          <t>51848; 80592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87941; 111093</t>
+          <t>89053; 112182</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13268; 29019</t>
+          <t>12703; 30511</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25665; 49114</t>
+          <t>27062; 49524</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18675; 37129</t>
+          <t>18393; 36223</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21680; 36690</t>
+          <t>22560; 37705</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26434; 50054</t>
+          <t>27250; 51433</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47305; 73057</t>
+          <t>47400; 74644</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41445; 71544</t>
+          <t>42180; 71605</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55285; 73851</t>
+          <t>55236; 74081</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44434; 72078</t>
+          <t>44250; 72372</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80050; 116311</t>
+          <t>80272; 116876</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64077; 97941</t>
+          <t>65877; 100224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83202; 106245</t>
+          <t>83076; 107702</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6463; 19893</t>
+          <t>5797; 19246</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14395; 33006</t>
+          <t>13697; 32630</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8454; 22317</t>
+          <t>8210; 23217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7481; 19295</t>
+          <t>7752; 19344</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11466; 28014</t>
+          <t>11595; 27495</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31866; 53228</t>
+          <t>31056; 54487</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29692; 53195</t>
+          <t>29704; 53634</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9699; 96364</t>
+          <t>10887; 98454</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21498; 42926</t>
+          <t>21694; 43171</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50625; 80038</t>
+          <t>51007; 80469</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42522; 70256</t>
+          <t>42484; 70178</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16759; 91697</t>
+          <t>20048; 95304</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7544; 20534</t>
+          <t>8239; 20497</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22539; 44415</t>
+          <t>21504; 43989</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15410; 32419</t>
+          <t>15042; 33149</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20638; 35537</t>
+          <t>20340; 36407</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32348; 55420</t>
+          <t>33348; 56334</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34646; 60736</t>
+          <t>35405; 60806</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33807; 61648</t>
+          <t>33981; 62779</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58530; 78768</t>
+          <t>57440; 79000</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43256; 72022</t>
+          <t>44317; 72583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64671; 99071</t>
+          <t>64301; 97030</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54794; 86554</t>
+          <t>55302; 86411</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82772; 109715</t>
+          <t>82657; 109354</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51447; 80020</t>
+          <t>51284; 80384</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>95990; 139114</t>
+          <t>97438; 137651</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74368; 105805</t>
+          <t>72292; 106074</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92960; 121889</t>
+          <t>92603; 123621</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>105422; 147546</t>
+          <t>105642; 146624</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>171276; 218887</t>
+          <t>172810; 223623</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>157095; 208522</t>
+          <t>160121; 212250</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>120404; 298399</t>
+          <t>123513; 300052</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166149; 217492</t>
+          <t>164711; 216682</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>276862; 341262</t>
+          <t>278494; 343070</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>244869; 307275</t>
+          <t>242771; 306347</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>237958; 397968</t>
+          <t>229064; 399571</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/LAWTONB_2R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R3-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,63; 24,84</t>
+          <t>11,26; 24,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 24,78</t>
+          <t>11,86; 25,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,17; 24,03</t>
+          <t>11,72; 24,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,49; 31,4</t>
+          <t>19,64; 30,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 25,93</t>
+          <t>11,19; 24,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,29; 34,13</t>
+          <t>19,76; 33,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,46; 31,21</t>
+          <t>17,66; 30,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,18; 39,08</t>
+          <t>30,61; 40,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,08; 22,22</t>
+          <t>13,34; 22,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,36; 27,88</t>
+          <t>18,04; 28,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,72; 25,99</t>
+          <t>16,82; 26,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,3; 34,39</t>
+          <t>26,74; 34,05</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 20,91</t>
+          <t>8,54; 20,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 31,98</t>
+          <t>17,55; 31,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,15; 21,96</t>
+          <t>11,84; 22,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 23,55</t>
+          <t>13,52; 22,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,92; 28,15</t>
+          <t>14,89; 27,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,76; 38,99</t>
+          <t>25,12; 38,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,25; 32,67</t>
+          <t>18,71; 32,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,39; 34,06</t>
+          <t>25,17; 34,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 22,03</t>
+          <t>13,53; 22,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,18; 33,75</t>
+          <t>23,31; 33,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,15; 26,09</t>
+          <t>16,93; 25,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,0; 28,52</t>
+          <t>21,44; 28,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 18,44</t>
+          <t>5,59; 18,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,22; 31,5</t>
+          <t>13,47; 31,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 20,18</t>
+          <t>6,94; 19,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 14,28</t>
+          <t>5,33; 13,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 20,24</t>
+          <t>8,51; 20,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 38,64</t>
+          <t>21,76; 37,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,83; 37,61</t>
+          <t>20,12; 36,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 27,36</t>
+          <t>19,97; 30,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 17,97</t>
+          <t>9,05; 18,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,85; 32,9</t>
+          <t>20,78; 32,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,49; 27,24</t>
+          <t>16,42; 27,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 19,24</t>
+          <t>13,82; 20,55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 14,94</t>
+          <t>6,04; 14,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 27,22</t>
+          <t>13,72; 28,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 18,98</t>
+          <t>8,99; 19,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,13; 18,14</t>
+          <t>10,09; 17,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,97; 26,98</t>
+          <t>15,13; 26,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,53; 24,95</t>
+          <t>14,92; 25,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,0; 25,86</t>
+          <t>13,9; 25,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,98; 28,86</t>
+          <t>21,52; 29,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,81; 20,98</t>
+          <t>12,9; 20,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,86; 23,94</t>
+          <t>16,0; 24,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,25; 20,7</t>
+          <t>13,14; 21,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,42; 23,05</t>
+          <t>17,66; 23,34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,21; 16,0</t>
+          <t>10,51; 16,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,41; 24,6</t>
+          <t>17,04; 24,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,23; 17,94</t>
+          <t>12,53; 17,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,37; 19,18</t>
+          <t>13,78; 18,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,66</t>
+          <t>15,63; 21,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,26; 30,1</t>
+          <t>23,09; 29,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,58; 27,28</t>
+          <t>20,29; 27,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 29,15</t>
+          <t>26,28; 30,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,97; 18,37</t>
+          <t>13,99; 18,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,38; 26,34</t>
+          <t>21,61; 26,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,73; 22,37</t>
+          <t>17,67; 22,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,69; 23,87</t>
+          <t>21,4; 24,62</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37371</t>
+          <t>39977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62521</t>
+          <t>66460</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99893</t>
+          <t>106437</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13368; 28563</t>
+          <t>12953; 28142</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16194; 34579</t>
+          <t>16548; 35564</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16634; 32855</t>
+          <t>16024; 33345</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28859; 46498</t>
+          <t>32071; 49448</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17740; 38769</t>
+          <t>16736; 35914</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33845; 56929</t>
+          <t>32958; 56103</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30281; 54115</t>
+          <t>30628; 53253</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53761; 69617</t>
+          <t>58105; 76198</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34610; 58769</t>
+          <t>35293; 60099</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56249; 85398</t>
+          <t>55264; 85935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51848; 80592</t>
+          <t>52162; 82163</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89053; 112182</t>
+          <t>94420; 120242</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>31636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>64286</t>
+          <t>70963</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93525</t>
+          <t>102599</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12703; 30511</t>
+          <t>12461; 29449</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27062; 49524</t>
+          <t>27181; 49543</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18393; 36223</t>
+          <t>19535; 37084</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22560; 37705</t>
+          <t>24086; 40519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27250; 51433</t>
+          <t>27198; 50794</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47400; 74644</t>
+          <t>48080; 74078</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42180; 71605</t>
+          <t>41003; 70534</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55236; 74081</t>
+          <t>60597; 81927</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44250; 72372</t>
+          <t>44452; 72315</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80272; 116876</t>
+          <t>80719; 114518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65877; 100224</t>
+          <t>65037; 98280</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83076; 107702</t>
+          <t>89802; 117708</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>43350</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52035</t>
+          <t>56959</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5797; 19246</t>
+          <t>5839; 18915</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13697; 32630</t>
+          <t>13958; 32752</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8210; 23217</t>
+          <t>7982; 22465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7752; 19344</t>
+          <t>8425; 21022</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11595; 27495</t>
+          <t>11556; 28369</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31056; 54487</t>
+          <t>30684; 53430</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29704; 53634</t>
+          <t>28687; 51757</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10887; 98454</t>
+          <t>34828; 52335</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21694; 43171</t>
+          <t>21739; 43508</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51007; 80469</t>
+          <t>50823; 79102</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42484; 70178</t>
+          <t>42307; 69885</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20048; 95304</t>
+          <t>45974; 68333</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27630</t>
+          <t>28317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>67625</t>
+          <t>74609</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95255</t>
+          <t>102925</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8239; 20497</t>
+          <t>8293; 20467</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21504; 43989</t>
+          <t>22173; 45417</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15042; 33149</t>
+          <t>15704; 33446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20340; 36407</t>
+          <t>21233; 36616</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33348; 56334</t>
+          <t>31597; 56043</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35405; 60806</t>
+          <t>36370; 62122</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33981; 62779</t>
+          <t>33739; 61139</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57440; 79000</t>
+          <t>63117; 86416</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44317; 72583</t>
+          <t>44624; 71824</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64301; 97030</t>
+          <t>64866; 97806</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55302; 86411</t>
+          <t>54839; 89294</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82657; 109354</t>
+          <t>88972; 117573</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106631</t>
+          <t>113539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>234077</t>
+          <t>255382</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>340708</t>
+          <t>368920</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51284; 80384</t>
+          <t>52804; 81300</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97438; 137651</t>
+          <t>95353; 138893</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72292; 106074</t>
+          <t>74075; 106225</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92603; 123621</t>
+          <t>97888; 130066</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>105642; 146624</t>
+          <t>105823; 147711</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>172810; 223623</t>
+          <t>171588; 219962</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>160121; 212250</t>
+          <t>157849; 210046</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>123513; 300052</t>
+          <t>236056; 274210</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164711; 216682</t>
+          <t>164992; 215710</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>278494; 343070</t>
+          <t>281438; 342188</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>242771; 306347</t>
+          <t>241978; 303179</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>229064; 399571</t>
+          <t>344204; 396063</t>
         </is>
       </c>
     </row>
